--- a/artfynd/A 15384-2026 artfynd.xlsx
+++ b/artfynd/A 15384-2026 artfynd.xlsx
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132928460</v>
+        <v>132929603</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,42 +1803,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582599</v>
+        <v>582603</v>
       </c>
       <c r="R12" t="n">
-        <v>7043956</v>
+        <v>7043928</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,12 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:53</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,22 +1887,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132929603</v>
+        <v>132928381</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,13 +1934,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582603</v>
+        <v>582595</v>
       </c>
       <c r="R13" t="n">
-        <v>7043928</v>
+        <v>7043954</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,22 +1994,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132928381</v>
+        <v>132928460</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,34 +2017,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582595</v>
+        <v>582599</v>
       </c>
       <c r="R14" t="n">
-        <v>7043954</v>
+        <v>7043956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2081,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2091,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,44 +2123,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132929699</v>
+        <v>132929366</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
@@ -2170,10 +2161,10 @@
         <v>582614</v>
       </c>
       <c r="R15" t="n">
-        <v>7043883</v>
+        <v>7043929</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2212,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,47 +2218,56 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132929366</v>
+        <v>132929699</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
@@ -2277,10 +2277,10 @@
         <v>582614</v>
       </c>
       <c r="R16" t="n">
-        <v>7043929</v>
+        <v>7043883</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,12 +2334,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 15384-2026 artfynd.xlsx
+++ b/artfynd/A 15384-2026 artfynd.xlsx
@@ -898,38 +898,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132928516</v>
+        <v>132918849</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582614</v>
+        <v>582572</v>
       </c>
       <c r="R4" t="n">
-        <v>7043964</v>
+        <v>7043799</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,49 +997,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132918849</v>
+        <v>132928516</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582572</v>
+        <v>582614</v>
       </c>
       <c r="R5" t="n">
-        <v>7043799</v>
+        <v>7043964</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 15384-2026 artfynd.xlsx
+++ b/artfynd/A 15384-2026 artfynd.xlsx
@@ -898,37 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132918849</v>
+        <v>132928516</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582572</v>
+        <v>582614</v>
       </c>
       <c r="R4" t="n">
-        <v>7043799</v>
+        <v>7043964</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,50 +998,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132928516</v>
+        <v>132918849</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582614</v>
+        <v>582572</v>
       </c>
       <c r="R5" t="n">
-        <v>7043964</v>
+        <v>7043799</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132929603</v>
+        <v>132928460</v>
       </c>
       <c r="B12" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,37 +1803,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582603</v>
+        <v>582599</v>
       </c>
       <c r="R12" t="n">
-        <v>7043928</v>
+        <v>7043956</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1877,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1897,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132928381</v>
+        <v>132929603</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,13 +1944,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582595</v>
+        <v>582603</v>
       </c>
       <c r="R13" t="n">
-        <v>7043954</v>
+        <v>7043928</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,22 +2004,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132928460</v>
+        <v>132928381</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,39 +2027,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582599</v>
+        <v>582595</v>
       </c>
       <c r="R14" t="n">
-        <v>7043956</v>
+        <v>7043954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2091,12 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:53</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2346,48 +2346,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132929765</v>
+        <v>132928312</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582608</v>
+        <v>582582</v>
       </c>
       <c r="R17" t="n">
-        <v>7043827</v>
+        <v>7043957</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2426,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,64 +2445,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132928312</v>
+        <v>132929765</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582582</v>
+        <v>582608</v>
       </c>
       <c r="R18" t="n">
-        <v>7043957</v>
+        <v>7043827</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,12 +2552,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 15384-2026 artfynd.xlsx
+++ b/artfynd/A 15384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132928519</v>
+        <v>132928047</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582597</v>
+        <v>582557</v>
       </c>
       <c r="R2" t="n">
-        <v>7043978</v>
+        <v>7043908</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132929745</v>
+        <v>132929765</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582609</v>
+        <v>582608</v>
       </c>
       <c r="R3" t="n">
-        <v>7043834</v>
+        <v>7043827</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132928516</v>
+        <v>132929793</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582614</v>
+        <v>582608</v>
       </c>
       <c r="R4" t="n">
-        <v>7043964</v>
+        <v>7043814</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,52 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132918849</v>
+        <v>132928275</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>92199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582572</v>
+        <v>582584</v>
       </c>
       <c r="R5" t="n">
-        <v>7043799</v>
+        <v>7043980</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132929793</v>
+        <v>132920065</v>
       </c>
       <c r="B6" t="n">
-        <v>91928</v>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582608</v>
+        <v>582565</v>
       </c>
       <c r="R6" t="n">
-        <v>7043814</v>
+        <v>7043895</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1191,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132929046</v>
+        <v>132919070</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582614</v>
+        <v>582550</v>
       </c>
       <c r="R7" t="n">
-        <v>7043931</v>
+        <v>7043815</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132928275</v>
+        <v>132928234</v>
       </c>
       <c r="B8" t="n">
-        <v>92651</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582584</v>
+        <v>582566</v>
       </c>
       <c r="R8" t="n">
-        <v>7043980</v>
+        <v>7043963</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,65 +1412,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132927409</v>
+        <v>132928381</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582554</v>
+        <v>582595</v>
       </c>
       <c r="R9" t="n">
-        <v>7043810</v>
+        <v>7043954</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,44 +1519,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132928145</v>
+        <v>132929366</v>
       </c>
       <c r="B10" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582574</v>
+        <v>582614</v>
       </c>
       <c r="R10" t="n">
-        <v>7043941</v>
+        <v>7043929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,57 +1638,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132929206</v>
+        <v>132919816</v>
       </c>
       <c r="B11" t="n">
-        <v>99140</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582618</v>
+        <v>582579</v>
       </c>
       <c r="R11" t="n">
-        <v>7043943</v>
+        <v>7043890</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132929603</v>
+        <v>132928145</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582603</v>
+        <v>582574</v>
       </c>
       <c r="R12" t="n">
-        <v>7043928</v>
+        <v>7043941</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,22 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132928460</v>
+        <v>132928237</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,42 +1863,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582599</v>
+        <v>582565</v>
       </c>
       <c r="R13" t="n">
-        <v>7043956</v>
+        <v>7043970</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1984,12 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,22 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132928381</v>
+        <v>132928519</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2051,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582595</v>
+        <v>582597</v>
       </c>
       <c r="R14" t="n">
-        <v>7043954</v>
+        <v>7043978</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,54 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132929699</v>
+        <v>132929603</v>
       </c>
       <c r="B15" t="n">
-        <v>99140</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582614</v>
+        <v>582603</v>
       </c>
       <c r="R15" t="n">
-        <v>7043883</v>
+        <v>7043928</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2202,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2212,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,35 +2173,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132929366</v>
+        <v>132928516</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
@@ -2277,10 +2216,10 @@
         <v>582614</v>
       </c>
       <c r="R16" t="n">
-        <v>7043929</v>
+        <v>7043964</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132929765</v>
+        <v>132919032</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,37 +2296,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582608</v>
+        <v>582546</v>
       </c>
       <c r="R17" t="n">
-        <v>7043827</v>
+        <v>7043836</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2426,7 +2370,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,49 +2390,50 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132928312</v>
+        <v>132919043</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2492,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582582</v>
+        <v>582561</v>
       </c>
       <c r="R18" t="n">
-        <v>7043957</v>
+        <v>7043822</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2487,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,15 +2507,1392 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132919076</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>582558</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7043820</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132927409</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>582554</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7043810</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132927484</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>582555</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7043817</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132928460</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>582599</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7043956</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132929046</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>582614</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7043931</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132918629</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>582607</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7043747</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132918849</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>582572</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7043799</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132919891</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>582574</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7043884</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132928312</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>582582</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7043957</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132929206</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>582618</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7043943</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132929699</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>582614</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7043883</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132929745</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>582609</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7043834</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15384-2026 artfynd.xlsx
+++ b/artfynd/A 15384-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928047</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929765</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920065</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919070</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928234</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928381</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929366</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919816</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928145</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928237</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928519</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929603</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928516</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919032</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919043</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2633,6 +2723,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919076</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927409</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,6 +2967,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132927484</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2984,6 +3089,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928460</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3101,6 +3211,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929046</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3212,6 +3327,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918629</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3323,6 +3443,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3434,6 +3559,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919891</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3545,6 +3675,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132928312</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3661,6 +3796,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929206</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929699</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3893,8 +4038,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132929745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>